--- a/data/trans_orig/P2A_enfcro_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2007</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91433</t>
+          <t>91256</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127750</t>
+          <t>128352</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>150859</t>
+          <t>148827</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>191751</t>
+          <t>189356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>250750</t>
+          <t>252168</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>308726</t>
+          <t>306593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>366314</t>
+          <t>365712</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>402631</t>
+          <t>402808</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275738</t>
+          <t>278133</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>316630</t>
+          <t>318662</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>652827</t>
+          <t>654960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710803</t>
+          <t>709385</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>177822</t>
+          <t>178912</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>226413</t>
+          <t>227543</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>248867</t>
+          <t>246486</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>296557</t>
+          <t>300908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>436318</t>
+          <t>440957</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>507626</t>
+          <t>511440</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>509076</t>
+          <t>507946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>557667</t>
+          <t>556577</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>328937</t>
+          <t>324586</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376627</t>
+          <t>379008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>853356</t>
+          <t>849542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>924664</t>
+          <t>920025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>189927</t>
+          <t>190037</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>239479</t>
+          <t>239704</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>329766</t>
+          <t>328385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>379142</t>
+          <t>380401</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>533865</t>
+          <t>533408</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>604381</t>
+          <t>606642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>399189</t>
+          <t>398964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>448741</t>
+          <t>448631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310602</t>
+          <t>309343</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>359978</t>
+          <t>361359</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>724031</t>
+          <t>721770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>794547</t>
+          <t>795004</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>221986</t>
+          <t>222053</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>271891</t>
+          <t>271745</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>306650</t>
+          <t>304049</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>349267</t>
+          <t>346266</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>539961</t>
+          <t>535624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>604149</t>
+          <t>602561</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,23%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>247256</t>
+          <t>247402</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>297161</t>
+          <t>297094</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>166375</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208992</t>
+          <t>211593</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>430640</t>
+          <t>432228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>494828</t>
+          <t>499165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,24%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>256194</t>
+          <t>255830</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>290891</t>
+          <t>291386</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>295418</t>
+          <t>297803</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>328197</t>
+          <t>329005</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>559575</t>
+          <t>560896</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>609887</t>
+          <t>608935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95819</t>
+          <t>95324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130516</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75789</t>
+          <t>74981</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108568</t>
+          <t>106183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>180809</t>
+          <t>181761</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231121</t>
+          <t>229800</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>209168</t>
+          <t>210607</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238012</t>
+          <t>238802</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>291414</t>
+          <t>291167</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>313717</t>
+          <t>313599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>509392</t>
+          <t>508545</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>545660</t>
+          <t>545501</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54571</t>
+          <t>53781</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83415</t>
+          <t>81976</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29217</t>
+          <t>29335</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51520</t>
+          <t>51767</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89857</t>
+          <t>90016</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126125</t>
+          <t>126972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172740</t>
+          <t>171716</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>191000</t>
+          <t>191035</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>286625</t>
+          <t>286994</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>310352</t>
+          <t>311341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>466842</t>
+          <t>465485</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>496230</t>
+          <t>496329</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18883</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37143</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23556</t>
+          <t>22567</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47283</t>
+          <t>46914</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47561</t>
+          <t>47462</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>76949</t>
+          <t>78306</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1395018</t>
+          <t>1395138</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1518207</t>
+          <t>1511228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1984896</t>
+          <t>1987034</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2100982</t>
+          <t>2098254</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3412677</t>
+          <t>3411780</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3580049</t>
+          <t>3578155</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1758336</t>
+          <t>1765315</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1881525</t>
+          <t>1881405</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1278215</t>
+          <t>1280943</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1394301</t>
+          <t>1392163</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3075692</t>
+          <t>3077586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3243064</t>
+          <t>3243961</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2012</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123093</t>
+          <t>123184</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162770</t>
+          <t>165010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>158409</t>
+          <t>156233</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>198141</t>
+          <t>197430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>292377</t>
+          <t>289400</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>348970</t>
+          <t>349107</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291376</t>
+          <t>289136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>331053</t>
+          <t>330962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232089</t>
+          <t>232800</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271821</t>
+          <t>273997</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>535406</t>
+          <t>535269</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>591999</t>
+          <t>594976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,28%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>239590</t>
+          <t>239270</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>290279</t>
+          <t>293360</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>262907</t>
+          <t>265574</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>315688</t>
+          <t>316133</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>517286</t>
+          <t>520991</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>590172</t>
+          <t>591151</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>396808</t>
+          <t>393727</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447497</t>
+          <t>447817</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>294567</t>
+          <t>294122</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347348</t>
+          <t>344681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>707170</t>
+          <t>706191</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>780056</t>
+          <t>776351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>252018</t>
+          <t>251479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>304209</t>
+          <t>305848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>378769</t>
+          <t>377266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>436003</t>
+          <t>435618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>641080</t>
+          <t>646264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>722806</t>
+          <t>723837</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,97%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>377654</t>
+          <t>376015</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>429845</t>
+          <t>430384</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>274847</t>
+          <t>275232</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332081</t>
+          <t>333584</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>669906</t>
+          <t>668875</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>751632</t>
+          <t>746448</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,6%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>281053</t>
+          <t>280090</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>333502</t>
+          <t>331090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>413677</t>
+          <t>412389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>459276</t>
+          <t>459808</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>705278</t>
+          <t>711396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>781942</t>
+          <t>783372</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,65%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>281115</t>
+          <t>283527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>333564</t>
+          <t>334527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156923</t>
+          <t>156391</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202522</t>
+          <t>203810</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>448874</t>
+          <t>447444</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>525538</t>
+          <t>519420</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,2%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>307313</t>
+          <t>307471</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>344657</t>
+          <t>342937</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>370872</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>400274</t>
+          <t>401725</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>683963</t>
+          <t>682927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>735899</t>
+          <t>733681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84772</t>
+          <t>86492</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122116</t>
+          <t>121958</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47526</t>
+          <t>46075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76928</t>
+          <t>77800</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141330</t>
+          <t>143548</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>193266</t>
+          <t>194302</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>276537</t>
+          <t>275984</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>295675</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>323020</t>
+          <t>322836</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>341077</t>
+          <t>341260</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>607860</t>
+          <t>604604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>633087</t>
+          <t>632646</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14111</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33249</t>
+          <t>33802</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30976</t>
+          <t>31160</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30695</t>
+          <t>31136</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55922</t>
+          <t>59178</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>229931</t>
+          <t>228793</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>243521</t>
+          <t>243440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>369596</t>
+          <t>368755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>383361</t>
+          <t>383400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>603976</t>
+          <t>604345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>623579</t>
+          <t>623912</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>20224</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34854</t>
+          <t>34485</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1789667</t>
+          <t>1787734</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1908688</t>
+          <t>1905940</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2346785</t>
+          <t>2344188</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2463521</t>
+          <t>2461200</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4170243</t>
+          <t>4171772</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4338258</t>
+          <t>4338291</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1518091</t>
+          <t>1520839</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1637112</t>
+          <t>1639045</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1094788</t>
+          <t>1097109</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1211524</t>
+          <t>1214121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2646830</t>
+          <t>2646797</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2814845</t>
+          <t>2813316</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2016</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104365</t>
+          <t>107039</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145598</t>
+          <t>145725</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>120352</t>
+          <t>118052</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>154476</t>
+          <t>155643</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>234816</t>
+          <t>236252</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>288828</t>
+          <t>288592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273865</t>
+          <t>273738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>315098</t>
+          <t>312424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>241279</t>
+          <t>240112</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275403</t>
+          <t>277703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>526390</t>
+          <t>526626</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>580402</t>
+          <t>578966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>147987</t>
+          <t>145675</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>194818</t>
+          <t>190982</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>200952</t>
+          <t>203871</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>248405</t>
+          <t>250822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>363084</t>
+          <t>360599</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>423663</t>
+          <t>424240</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>395678</t>
+          <t>399514</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>442509</t>
+          <t>444821</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>315139</t>
+          <t>312722</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362592</t>
+          <t>359673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730377</t>
+          <t>729800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>790956</t>
+          <t>793441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>200377</t>
+          <t>201296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>248854</t>
+          <t>250081</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>290588</t>
+          <t>292317</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>339675</t>
+          <t>340798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>502184</t>
+          <t>499876</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>577069</t>
+          <t>572595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>420243</t>
+          <t>419016</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>468720</t>
+          <t>467801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321711</t>
+          <t>320588</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>370798</t>
+          <t>369069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>753414</t>
+          <t>757888</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>828299</t>
+          <t>830607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,43%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>309020</t>
+          <t>306405</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>362434</t>
+          <t>362341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>358781</t>
+          <t>358495</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>408657</t>
+          <t>409580</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>684552</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>753721</t>
+          <t>752920</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283614</t>
+          <t>283707</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>337028</t>
+          <t>339643</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>240420</t>
+          <t>239497</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290296</t>
+          <t>290582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>541404</t>
+          <t>542205</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>610573</t>
+          <t>613935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,4%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>282765</t>
+          <t>281898</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>327472</t>
+          <t>327353</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>368652</t>
+          <t>370652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>410506</t>
+          <t>410010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>665893</t>
+          <t>663331</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>726854</t>
+          <t>727680</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,65%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150446</t>
+          <t>150565</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195153</t>
+          <t>196020</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86343</t>
+          <t>86839</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128197</t>
+          <t>126197</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247913</t>
+          <t>247087</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308874</t>
+          <t>311436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>279764</t>
+          <t>277538</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>304371</t>
+          <t>303031</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>323356</t>
+          <t>322016</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>347551</t>
+          <t>348230</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>607957</t>
+          <t>608813</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>643698</t>
+          <t>644600</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>31299</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54566</t>
+          <t>56792</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30211</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54406</t>
+          <t>55746</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68394</t>
+          <t>67492</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104135</t>
+          <t>103279</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>230263</t>
+          <t>230513</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>246004</t>
+          <t>245677</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>374646</t>
+          <t>374482</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>392338</t>
+          <t>392297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>611646</t>
+          <t>611449</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>633801</t>
+          <t>633949</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>11321</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>26485</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25523</t>
+          <t>25687</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>23218</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45521</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1628133</t>
+          <t>1629433</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1749665</t>
+          <t>1743343</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2113439</t>
+          <t>2119804</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2230684</t>
+          <t>2232713</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3773554</t>
+          <t>3775991</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3942718</t>
+          <t>3938798</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,76%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1644685</t>
+          <t>1651007</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1766217</t>
+          <t>1764917</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1313858</t>
+          <t>1311829</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1431103</t>
+          <t>1424738</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2996174</t>
+          <t>3000094</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3165338</t>
+          <t>3162901</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2023</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74207</t>
+          <t>73647</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>139246</t>
+          <t>137071</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55945</t>
+          <t>55979</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99341</t>
+          <t>97367</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>143356</t>
+          <t>141077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>222345</t>
+          <t>219613</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260741</t>
+          <t>262916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>325780</t>
+          <t>326340</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213859</t>
+          <t>215833</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257255</t>
+          <t>257221</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>490842</t>
+          <t>493574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569831</t>
+          <t>572110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73994</t>
+          <t>74033</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119949</t>
+          <t>118489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60670</t>
+          <t>61878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125077</t>
+          <t>128697</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>147554</t>
+          <t>152030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>232951</t>
+          <t>233633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>303598</t>
+          <t>305058</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>349553</t>
+          <t>349514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>383396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>451423</t>
+          <t>450215</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702689</t>
+          <t>702007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>788086</t>
+          <t>783610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89443</t>
+          <t>93892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129382</t>
+          <t>131896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109890</t>
+          <t>106163</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163000</t>
+          <t>165207</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>212197</t>
+          <t>218069</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279901</t>
+          <t>282864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406956</t>
+          <t>404442</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>446895</t>
+          <t>442446</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>429002</t>
+          <t>426795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>482112</t>
+          <t>485839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>848439</t>
+          <t>845476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>916143</t>
+          <t>910271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86602</t>
+          <t>88841</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>281597</t>
+          <t>281689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>207982</t>
+          <t>203870</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>271162</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>257140</t>
+          <t>279231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>533278</t>
+          <t>536158</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>606189</t>
+          <t>606097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>801184</t>
+          <t>798945</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>442309</t>
+          <t>441719</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>504899</t>
+          <t>509011</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1067389</t>
+          <t>1064509</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1343527</t>
+          <t>1321436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>227409</t>
+          <t>225426</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>269768</t>
+          <t>268867</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>254204</t>
+          <t>254810</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>288488</t>
+          <t>290551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>490256</t>
+          <t>492879</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>545195</t>
+          <t>548653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,47%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>291466</t>
+          <t>292367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>333825</t>
+          <t>335808</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>259417</t>
+          <t>257354</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>293701</t>
+          <t>293095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>563944</t>
+          <t>560486</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>618883</t>
+          <t>616260</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,56%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>157174</t>
+          <t>159126</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>188153</t>
+          <t>189331</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>353602</t>
+          <t>354558</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>538015</t>
+          <t>534162</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>513816</t>
+          <t>514853</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>780780</t>
+          <t>786726</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180012</t>
+          <t>178834</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>210991</t>
+          <t>209039</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70353</t>
+          <t>74206</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254766</t>
+          <t>253810</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>195753</t>
+          <t>189807</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>462717</t>
+          <t>461680</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>166518</t>
+          <t>165908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>193348</t>
+          <t>192139</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>270419</t>
+          <t>270246</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>298859</t>
+          <t>297632</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>446703</t>
+          <t>445883</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>487261</t>
+          <t>481664</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>67,97%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89411</t>
+          <t>90620</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>116241</t>
+          <t>116851</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>126972</t>
+          <t>128199</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155412</t>
+          <t>155585</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>221329</t>
+          <t>226926</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>261887</t>
+          <t>262707</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>878030</t>
+          <t>851461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1217031</t>
+          <t>1212100</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1417449</t>
+          <t>1412102</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1988813</t>
+          <t>1968520</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2415351</t>
+          <t>2428411</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3070970</t>
+          <t>3056824</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2242786</t>
+          <t>2247717</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2581787</t>
+          <t>2608356</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1723467</t>
+          <t>1743760</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2294831</t>
+          <t>2300178</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4101127</t>
+          <t>4115273</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4756746</t>
+          <t>4743686</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_enfcro_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91256</t>
+          <t>91985</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128352</t>
+          <t>127017</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148827</t>
+          <t>150687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>189356</t>
+          <t>193048</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>252168</t>
+          <t>255463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>306593</t>
+          <t>306021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>365712</t>
+          <t>367047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>402808</t>
+          <t>402079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278133</t>
+          <t>274441</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>318662</t>
+          <t>316802</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>654960</t>
+          <t>655532</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>709385</t>
+          <t>706090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,43%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178912</t>
+          <t>180843</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>227543</t>
+          <t>227973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>246486</t>
+          <t>244944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>300908</t>
+          <t>296054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>440957</t>
+          <t>439961</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>511440</t>
+          <t>508667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>507946</t>
+          <t>507516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>556577</t>
+          <t>554646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324586</t>
+          <t>329440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>379008</t>
+          <t>380550</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>849542</t>
+          <t>852315</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920025</t>
+          <t>921021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,67%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>190037</t>
+          <t>188875</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>239704</t>
+          <t>237957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>328385</t>
+          <t>328624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>380401</t>
+          <t>379396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>533408</t>
+          <t>531057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>606642</t>
+          <t>605935</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>398964</t>
+          <t>400711</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>448631</t>
+          <t>449793</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>309343</t>
+          <t>310348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>361359</t>
+          <t>361120</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>721770</t>
+          <t>722477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>795004</t>
+          <t>797355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>222053</t>
+          <t>220660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>271745</t>
+          <t>268461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>304049</t>
+          <t>306104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>346266</t>
+          <t>348783</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>535624</t>
+          <t>538133</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>602561</t>
+          <t>602614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>247402</t>
+          <t>250686</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>297094</t>
+          <t>298487</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169376</t>
+          <t>166859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>211593</t>
+          <t>209538</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>432228</t>
+          <t>432175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>499165</t>
+          <t>496656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,0%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>255830</t>
+          <t>256596</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>291386</t>
+          <t>292789</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>297803</t>
+          <t>295301</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>329005</t>
+          <t>328300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>560896</t>
+          <t>561809</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>608935</t>
+          <t>610627</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95324</t>
+          <t>93921</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130880</t>
+          <t>130114</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74981</t>
+          <t>75686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106183</t>
+          <t>108685</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181761</t>
+          <t>180069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>229800</t>
+          <t>228887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>210607</t>
+          <t>209933</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238802</t>
+          <t>238314</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>291167</t>
+          <t>291603</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>313599</t>
+          <t>314592</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>508545</t>
+          <t>510264</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>545501</t>
+          <t>546768</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53781</t>
+          <t>54269</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81976</t>
+          <t>82650</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29335</t>
+          <t>28342</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51767</t>
+          <t>51331</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90016</t>
+          <t>88749</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126972</t>
+          <t>125253</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>171716</t>
+          <t>171313</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>191035</t>
+          <t>190789</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>286994</t>
+          <t>286407</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>311341</t>
+          <t>310181</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>465485</t>
+          <t>467599</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>496329</t>
+          <t>497282</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>19094</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>38570</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22567</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46914</t>
+          <t>47501</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47462</t>
+          <t>46509</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78306</t>
+          <t>76192</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1395138</t>
+          <t>1400719</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1511228</t>
+          <t>1511926</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1987034</t>
+          <t>1983020</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2098254</t>
+          <t>2093417</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3411780</t>
+          <t>3414949</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3578155</t>
+          <t>3578136</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1765315</t>
+          <t>1764617</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1881405</t>
+          <t>1875824</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1280943</t>
+          <t>1285780</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1392163</t>
+          <t>1396177</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3077586</t>
+          <t>3077605</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3243961</t>
+          <t>3240792</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123184</t>
+          <t>124490</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>165010</t>
+          <t>163616</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>156233</t>
+          <t>155975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>197430</t>
+          <t>196184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>289400</t>
+          <t>291849</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>349107</t>
+          <t>350123</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289136</t>
+          <t>290530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>330962</t>
+          <t>329656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232800</t>
+          <t>234046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273997</t>
+          <t>274255</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>535269</t>
+          <t>534253</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>594976</t>
+          <t>592527</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>239270</t>
+          <t>240174</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>293360</t>
+          <t>291682</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>265574</t>
+          <t>264883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>316133</t>
+          <t>313605</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>520991</t>
+          <t>517434</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>591151</t>
+          <t>588107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393727</t>
+          <t>395405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447817</t>
+          <t>446913</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>294122</t>
+          <t>296650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>344681</t>
+          <t>345372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>706191</t>
+          <t>709235</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>776351</t>
+          <t>779908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,12%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>251479</t>
+          <t>253277</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>305848</t>
+          <t>307185</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>377266</t>
+          <t>377832</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>435618</t>
+          <t>432002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>646264</t>
+          <t>644961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>723837</t>
+          <t>721484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,8%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>376015</t>
+          <t>374678</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>430384</t>
+          <t>428586</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>275232</t>
+          <t>278848</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333584</t>
+          <t>333018</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>668875</t>
+          <t>671228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>746448</t>
+          <t>747751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>280090</t>
+          <t>279954</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>331090</t>
+          <t>333256</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>412389</t>
+          <t>412184</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>459808</t>
+          <t>460113</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>711396</t>
+          <t>708757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>783372</t>
+          <t>779917</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283527</t>
+          <t>281361</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>334527</t>
+          <t>334663</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156391</t>
+          <t>156086</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>203810</t>
+          <t>204015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>447444</t>
+          <t>450899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>519420</t>
+          <t>522059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,42%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>307471</t>
+          <t>305921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>342937</t>
+          <t>342907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>370806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>401725</t>
+          <t>400615</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>682927</t>
+          <t>683946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>733681</t>
+          <t>732884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86492</t>
+          <t>86522</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121958</t>
+          <t>123508</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46075</t>
+          <t>47185</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77800</t>
+          <t>76994</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143548</t>
+          <t>144345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194302</t>
+          <t>193283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>275984</t>
+          <t>276145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>295366</t>
+          <t>295821</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>322836</t>
+          <t>324165</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>341260</t>
+          <t>341990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>604604</t>
+          <t>606725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>632646</t>
+          <t>633511</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>13965</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33802</t>
+          <t>33641</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12736</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31160</t>
+          <t>29831</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31136</t>
+          <t>30271</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59178</t>
+          <t>57057</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228793</t>
+          <t>230019</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>243440</t>
+          <t>243683</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>368755</t>
+          <t>368176</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>383400</t>
+          <t>383240</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>604345</t>
+          <t>602749</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>623912</t>
+          <t>623370</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21058</t>
+          <t>19832</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34485</t>
+          <t>36081</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1787734</t>
+          <t>1781529</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1905940</t>
+          <t>1911230</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2344188</t>
+          <t>2343467</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2461200</t>
+          <t>2459148</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4171772</t>
+          <t>4164479</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4338291</t>
+          <t>4334381</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,05%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1520839</t>
+          <t>1515549</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1639045</t>
+          <t>1645250</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1097109</t>
+          <t>1099161</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1214121</t>
+          <t>1214842</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2646797</t>
+          <t>2650707</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2813316</t>
+          <t>2820609</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>107039</t>
+          <t>106069</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145725</t>
+          <t>144793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118052</t>
+          <t>118646</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155643</t>
+          <t>154134</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>236252</t>
+          <t>231751</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>288592</t>
+          <t>287935</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273738</t>
+          <t>274670</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>312424</t>
+          <t>313394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240112</t>
+          <t>241621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277703</t>
+          <t>277109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>526626</t>
+          <t>527283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578966</t>
+          <t>583467</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,57%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>145675</t>
+          <t>146280</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>190982</t>
+          <t>190379</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>203871</t>
+          <t>202115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>250822</t>
+          <t>247449</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>360599</t>
+          <t>364820</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>424240</t>
+          <t>425889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399514</t>
+          <t>400117</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>444821</t>
+          <t>444216</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>312722</t>
+          <t>316095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359673</t>
+          <t>361429</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729800</t>
+          <t>728151</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>793441</t>
+          <t>789220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>201296</t>
+          <t>198542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>250081</t>
+          <t>250507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>292317</t>
+          <t>291839</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>340798</t>
+          <t>340489</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>499876</t>
+          <t>504296</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>572595</t>
+          <t>576983</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>419016</t>
+          <t>418590</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467801</t>
+          <t>470555</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>320588</t>
+          <t>320897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>369069</t>
+          <t>369547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>757888</t>
+          <t>753500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>830607</t>
+          <t>826187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>306405</t>
+          <t>306475</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>362341</t>
+          <t>360355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>358495</t>
+          <t>356075</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>409580</t>
+          <t>407706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>680637</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>752920</t>
+          <t>750975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283707</t>
+          <t>285693</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>339643</t>
+          <t>339573</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239497</t>
+          <t>241371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290582</t>
+          <t>293002</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>542205</t>
+          <t>544150</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>613935</t>
+          <t>614488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>281898</t>
+          <t>284094</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>327353</t>
+          <t>326517</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>370652</t>
+          <t>368906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>410010</t>
+          <t>410255</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>663331</t>
+          <t>664408</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>727680</t>
+          <t>723752</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150565</t>
+          <t>151401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196020</t>
+          <t>193824</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86839</t>
+          <t>86594</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126197</t>
+          <t>127943</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247087</t>
+          <t>251015</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>311436</t>
+          <t>310359</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>277538</t>
+          <t>277628</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>303031</t>
+          <t>302649</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>322016</t>
+          <t>321662</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>348230</t>
+          <t>347705</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>608813</t>
+          <t>607951</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>644600</t>
+          <t>644970</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31299</t>
+          <t>31681</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56792</t>
+          <t>56702</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>30057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55746</t>
+          <t>56100</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67492</t>
+          <t>67122</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103279</t>
+          <t>104141</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>230513</t>
+          <t>230588</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>245677</t>
+          <t>245549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>374482</t>
+          <t>373228</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>392297</t>
+          <t>391234</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>611449</t>
+          <t>611285</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>633949</t>
+          <t>633817</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11321</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26485</t>
+          <t>26410</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25687</t>
+          <t>26941</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23218</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45882</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1629433</t>
+          <t>1624172</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1743343</t>
+          <t>1744035</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2119804</t>
+          <t>2111362</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2232713</t>
+          <t>2229526</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3775991</t>
+          <t>3777097</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3938798</t>
+          <t>3939736</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,78%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1651007</t>
+          <t>1650315</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1764917</t>
+          <t>1770178</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1311829</t>
+          <t>1315016</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1424738</t>
+          <t>1433180</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3000094</t>
+          <t>2999156</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3162901</t>
+          <t>3161795</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>103437</t>
+          <t>83223</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73647</t>
+          <t>58540</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>137071</t>
+          <t>112036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>74660</t>
+          <t>82561</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55979</t>
+          <t>60582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97367</t>
+          <t>105128</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>178097</t>
+          <t>165784</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141077</t>
+          <t>134791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>219613</t>
+          <t>204494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>296550</t>
+          <t>324570</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262916</t>
+          <t>295757</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>326340</t>
+          <t>349253</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>238540</t>
+          <t>279951</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215833</t>
+          <t>257384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257221</t>
+          <t>301930</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>535090</t>
+          <t>604521</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>493574</t>
+          <t>565811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>572110</t>
+          <t>635514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>82,5%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>95938</t>
+          <t>99973</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74033</t>
+          <t>79298</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118489</t>
+          <t>124491</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>100977</t>
+          <t>109218</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61878</t>
+          <t>91909</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128697</t>
+          <t>129288</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>196915</t>
+          <t>209192</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152030</t>
+          <t>178861</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>233633</t>
+          <t>239178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>327609</t>
+          <t>376917</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>305058</t>
+          <t>352399</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>349514</t>
+          <t>397592</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>411116</t>
+          <t>392515</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>383396</t>
+          <t>372445</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>450215</t>
+          <t>409824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>738725</t>
+          <t>769431</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702007</t>
+          <t>739445</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>783610</t>
+          <t>799762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>81,72%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,102 +10351,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>110297</t>
+          <t>123071</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93892</t>
+          <t>103179</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131896</t>
+          <t>142858</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>19,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>158176</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>140838</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>177174</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>25,38%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>22,6%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>281247</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>255788</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>307664</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>22,61%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>20,56%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>142068</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>106163</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>165207</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>24,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>17,93%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>27,91%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>252365</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>218069</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>282864</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>22,37%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>19,33%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -10464,102 +10464,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>426041</t>
+          <t>497766</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>404442</t>
+          <t>477979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>442446</t>
+          <t>517658</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>80,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>83,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>465017</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>446019</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>482355</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>74,62%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>71,57%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>77,4%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1057</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>962782</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>936365</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>988241</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>77,39%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>75,27%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>79,44%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>82,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>449934</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>426795</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>485839</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>76,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>72,09%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>82,07%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1057</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>875975</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>845476</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>910271</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>77,63%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>74,93%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>194400</t>
+          <t>209883</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88841</t>
+          <t>186479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>238021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>246553</t>
+          <t>263262</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>203870</t>
+          <t>241941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>271162</t>
+          <t>282356</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>440954</t>
+          <t>473145</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>279231</t>
+          <t>441939</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>536158</t>
+          <t>504260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>693386</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>606097</t>
+          <t>462596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>798945</t>
+          <t>514138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>466328</t>
+          <t>473624</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>441719</t>
+          <t>454530</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>509011</t>
+          <t>494945</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1159713</t>
+          <t>964359</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1064509</t>
+          <t>933244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1321436</t>
+          <t>995565</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>247077</t>
+          <t>260866</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>225426</t>
+          <t>237119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>268867</t>
+          <t>284947</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>272289</t>
+          <t>301859</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>254810</t>
+          <t>282713</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>290551</t>
+          <t>321582</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>519366</t>
+          <t>562726</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>492879</t>
+          <t>534478</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>548653</t>
+          <t>596354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>314157</t>
+          <t>348480</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>292367</t>
+          <t>324399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335808</t>
+          <t>372227</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>275616</t>
+          <t>306996</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>257354</t>
+          <t>287273</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>293095</t>
+          <t>326142</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>589773</t>
+          <t>655476</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>560486</t>
+          <t>621848</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>616260</t>
+          <t>683724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>56,13%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>173558</t>
+          <t>189240</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>159126</t>
+          <t>172157</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>189331</t>
+          <t>206063</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>443732</t>
+          <t>260916</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>354558</t>
+          <t>245590</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>534162</t>
+          <t>276126</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>617290</t>
+          <t>450155</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>514853</t>
+          <t>426650</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>786726</t>
+          <t>473937</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>56,0%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>194607</t>
+          <t>217840</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178834</t>
+          <t>201017</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>209039</t>
+          <t>234923</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>164636</t>
+          <t>178250</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74206</t>
+          <t>163040</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>253810</t>
+          <t>193576</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>359243</t>
+          <t>396091</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>189807</t>
+          <t>372309</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>461680</t>
+          <t>419596</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>179994</t>
+          <t>195743</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>165908</t>
+          <t>181690</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>192139</t>
+          <t>211035</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>284513</t>
+          <t>307533</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>270246</t>
+          <t>292603</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>297632</t>
+          <t>322168</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>464507</t>
+          <t>503276</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>445883</t>
+          <t>483633</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>481664</t>
+          <t>524949</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,75%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>102765</t>
+          <t>114455</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90620</t>
+          <t>99163</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>116851</t>
+          <t>128508</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>141318</t>
+          <t>157076</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128199</t>
+          <t>142441</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155585</t>
+          <t>172006</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>244083</t>
+          <t>271531</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>226926</t>
+          <t>249858</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>262707</t>
+          <t>291174</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1104702</t>
+          <t>1162000</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>851461</t>
+          <t>1106345</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1212100</t>
+          <t>1221352</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1564793</t>
+          <t>1483525</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1412102</t>
+          <t>1433536</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1968520</t>
+          <t>1533086</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2669494</t>
+          <t>2645524</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2428411</t>
+          <t>2567115</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3056824</t>
+          <t>2736520</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2355115</t>
+          <t>2370762</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2247717</t>
+          <t>2311410</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2608356</t>
+          <t>2426417</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2147487</t>
+          <t>2253429</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1743760</t>
+          <t>2203868</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2300178</t>
+          <t>2303418</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4502603</t>
+          <t>4624192</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4115273</t>
+          <t>4533196</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4743686</t>
+          <t>4702601</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>64,69%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_enfcro_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
